--- a/artfynd/A 39289-2021 artfynd.xlsx
+++ b/artfynd/A 39289-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 39289-2021 artfynd.xlsx
+++ b/artfynd/A 39289-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109195480</v>
+        <v>65427472</v>
       </c>
       <c r="B2" t="n">
-        <v>97921</v>
+        <v>80461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,33 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224363</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kaalama, 900 m SV-VSV om, Nb</t>
+          <t>Aareavaara, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>858233</v>
+        <v>858060</v>
       </c>
       <c r="R2" t="n">
-        <v>7513020</v>
+        <v>7513147</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -736,17 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1997-07-24</t>
+          <t>2015-09-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1997-07-24</t>
+          <t>2015-09-06</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Norrbottens flora - 2010.  Medobservatör Claire Lewis.</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -758,23 +762,237 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>gles tallskogssluttning</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>109195480</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98062</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kaalama, 900 m SV-VSV om, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>858233</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7513020</v>
+      </c>
+      <c r="S3" t="n">
+        <v>100</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1997-07-24</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1997-07-24</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Norrbottens flora - 2010.  Medobservatör Claire Lewis.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>gles tallskogssluttning</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Mora Aronsson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Lennart Stenberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Norrbottens flora 2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120889656</v>
+      </c>
+      <c r="B4" t="n">
+        <v>103902</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>225176</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Finnvide</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Salix bebbiana</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sarg.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>900 m SV-VSV om Kaalama, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>858233</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7513020</v>
+      </c>
+      <c r="S4" t="n">
+        <v>100</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1997-07-24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1997-07-24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Norrbottens flora - 2010. Medobservatör Claire Lewis. Belägg hos Lennart Stenberg.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>gles tallskogssluttning</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>nb97 0832</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lennart Stenberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Norrbottens flora 2010</t>
         </is>

--- a/artfynd/A 39289-2021 artfynd.xlsx
+++ b/artfynd/A 39289-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65427472</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
           <t>Norrbottens flora 2010</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109195480</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,8 +1012,18 @@
           <t>Norrbottens flora 2010</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120889656</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>